--- a/cutsclothing/cutsclothing_5_upgraded_products.xlsx
+++ b/cutsclothing/cutsclothing_5_upgraded_products.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,6 +160,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,35 +571,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Current Word Count</t>
+          <t>Feed Word Count (Shopify API)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Live Storefront Words (Theme)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Diagnostic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Upgraded Description (Clean Readable Text + Specs)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Current Alt Text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Image Alt Text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Google Shopping Category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Smart Tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Live Product URL</t>
         </is>
@@ -622,45 +633,53 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Crossover Active Tee | Charcoal Signature-Fit - Tailored Cut</t>
+          <t>Cuts Clothing Crossover Active Tee - Charcoal Signature Fit</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>The Crossover Active Tee | Charcoal Signature-Fit by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginCutsclothing (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F2" s="7" t="n">
+        <v>223</v>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
+          <t>Standard Catalog Item</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Experience the perfect fusion of athletic performance and everyday style with our breathable, curve-hem active tee. Engineered for movement, this shirt keeps you cool and comfortable from your morning workout to your evening commute.
+Key Features &amp; Benefits
+• Breathable cotton-forward fabric blend for all-day airflow.
+• Signature-Fit cut offers a modern, tailored aesthetic without restriction.
+• Curved-hem design provides an elongated, flattering silhouette.
+• Tagless interior construction eliminates irritation and chafing.
+• Versatile moisture-wicking properties for active and casual wear.
+Material: Performance Cotton Blend | Fit: Signature-Fit | Care: Machine Wash Cold</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Crossover Active Tee | Charcoal Signature-Fit - Cutsclothing Official Product View</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Model wearing a charcoal Cuts Clothing Crossover Active Tee with a curved hem design</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Shirts &amp; Tops</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>Activewear, T-Shirts, Charcoal, Mens Apparel, Performance Gear</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>https://cutsclothing.com/products/crossover-tee-charcoal</t>
         </is>
@@ -684,45 +703,53 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Icon Pull-On Pant | Sepia Tint Classic-Fit Enduratech™ | Handcrafted Artisanal Collection</t>
+          <t>Cuts Clothing Icon Pull-On Cropped Pant - Sepia Tint</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>The Icon Pull-On Pant | Sepia Tint Classic-Fit Enduratech™ by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Artisanal Craftsmanship: Individually crafted using premium, heirloom-grade materials for enduring durability.
-• Timeless Functional Design: Balances modern aesthetics with ergonomic daily utility for home and living spaces.
-• Sustainable Sourcing: Built responsibly with low-impact manufacturing and non-toxic, food-safe finishes.
-• Signature Heritage Quality: Engineered to withstand everyday wear while maintaining distinctive character.
-Technical Specifications
-Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginCutsclothing (United States)Design StandardTimeless Modern Functionalism</t>
-        </is>
+      <c r="F3" s="7" t="n">
+        <v>201</v>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Upgrade your daily wardrobe with the Icon Pull-On Pant, featuring our proprietary Enduratech fabric for unmatched durability and stretch. This cropped-fit trouser delivers a relaxed, refined look that transitions effortlessly between professional and casual settings.
+Key Features &amp; Benefits
+• Enduratech fabric provides premium 4-way stretch and wrinkle resistance.
+• Modern cropped-leg length offers a contemporary, stylish profile.
+• Easy-wear pull-on elastic waistband ensures maximum daily comfort.
+• Durable construction maintains shape through repeated washes.
+• Deep pockets provide secure storage for your daily essentials.
+Material: Enduratech Fabric | Fit: Classic-Fit Cropped | Style: Pull-On Trouser</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Icon Pull-On Pant | Sepia Tint Classic-Fit Enduratech™ - Cutsclothing Official Product View</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Home &amp; Garden &gt; Furniture</t>
-        </is>
-      </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
+          <t>Cuts Clothing Icon Pull-On Cropped Pant in Sepia Tint colorway</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Pants</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Pants, Casual Wear, Enduratech, Mens Bottoms, Cropped</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>https://cutsclothing.com/products/icon-pull-on-cropped-pant-sepia-tint</t>
         </is>
@@ -746,45 +773,53 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AO Long Sleeve Polo | White Signature-Fit PYCA Pro® - Tailored Cut</t>
+          <t>Cuts Clothing AO Long Sleeve Polo - White PYCA Pro</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>The AO Long Sleeve Polo | White Signature-Fit PYCA Pro® by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginCutsclothing (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F4" s="7" t="n">
+        <v>194</v>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
+          <t>Standard Catalog Item</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Achieve a polished look that never compromises on comfort with the versatile AO Long Sleeve Polo. Crafted from high-performance PYCA Pro fabric, this essential piece resists wrinkles and keeps you looking sharp from morning meetings to weekend events.
+Key Features &amp; Benefits
+• PYCA Pro fabric offers lightweight comfort and professional structure.
+• Wrinkle-resistant material ensures a crisp look throughout the day.
+• Long sleeve design provides excellent coverage and layering versatility.
+• Signature-Fit tailoring creates a sleek, flattering profile.
+• Minimalist aesthetic pairs perfectly with trousers or denim.
+Material: PYCA Pro | Fit: Signature-Fit | Style: Long Sleeve Polo</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>AO Long Sleeve Polo | White Signature-Fit PYCA Pro® - Cutsclothing Official Product View</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Cuts Clothing white AO long sleeve polo shirt featuring PYCA Pro fabric</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Shirts &amp; Tops</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Polos, Long Sleeve, White, Mens Apparel, Business Casual</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>https://cutsclothing.com/products/ao-l-s-polo-white</t>
         </is>
@@ -808,45 +843,53 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The 9-to-Cozy Fit: Oversized - Tailored Cut</t>
+          <t>Cuts Women's 9-to-Cozy Fleece Oversized Bundle</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>The The 9-to-Cozy Fit: Oversized by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginCutsclothing (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F5" s="7" t="n">
+        <v>248</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
+          <t>Standard Catalog Item</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Elevate your lounge rotation with the full Divine Fleece set, designed for maximum softness and a relaxed oversized fit. This curated bundle gives you the ultimate matching comfort experience while offering exceptional value.
+Key Features &amp; Benefits
+• Buttery-soft fleece material provides premium warmth and comfort.
+• Bundle includes oversized hoodie, quarter-zip, and matching sweatpants.
+• Relaxed, modern cut designed for high-end lounging and layering.
+• Versatile separates that can be styled individually or as a set.
+• High-quality fabric construction designed for lasting softness.
+Material: Divine Fleece | Fit: Oversized | Bundle: 3-Piece Set</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>The 9-to-Cozy Fit: Oversized - Cutsclothing Official Product View</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Women's 9-to-Cozy bundle featuring Divine Fleece hoodie, quarter-zip, and sweatpants</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Clothing Sets</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Womenswear, Lounge Sets, Fleece, Bundle, Oversized</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>https://cutsclothing.com/products/womens-divine-fleece-oversized-hoodie-q-zip-sweatpant-fit-bundle</t>
         </is>
@@ -870,45 +913,53 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>The Overtime Fit: Boxed Crop Tee + Foundation-Air Trouser - Tailored Cut</t>
+          <t>Cuts The Overtime Fit: Boxed Tee &amp; Pleated Trouser Bundle</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>The The Overtime Fit: Boxed Crop Tee + Foundation-Air Trouser by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginCutsclothing (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F6" s="7" t="n">
+        <v>68</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Master the art of effortless, elevated style with this hand-picked lookbook ensemble featuring our signature Boxed Crop Tee and Foundation-Air Trouser. This sharp, minimalist combination is designed to make dressing for any occasion perfectly simple.
+Key Features &amp; Benefits
+• Curated bundle includes the Boxed Crop Tee and Relaxed Pleated Trouser.
+• Foundation-Air fabric offers lightweight, breathable performance.
+• Boxed Crop Tee silhouette creates a modern, structured aesthetic.
+• Pleated trousers provide a sophisticated, relaxed professional look.
+• Pre-styled combination saves time and ensures a cohesive outfit.
+Material: Foundation-Air / Signature Fabric | Fit: Relaxed / Boxed | Style: Elevated Casual</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>The Overtime Fit: Boxed Crop Tee + Foundation-Air Trouser - Cutsclothing Official Product View</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Full outfit bundle featuring the Overtime Boxed Crop Tee and Foundation-Air Pleated Trousers</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Clothing Sets</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Menswear, Bundles, Pleated Pants, Crop Tee, Streetwear</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>https://cutsclothing.com/products/overtime-boxed-tee-foundation-air-fit-bundle</t>
         </is>
@@ -967,892 +1018,842 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Body (HTML)</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Option1 Name</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Option1 Value</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Variant SKU</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Variant Grams</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Tracker</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Qty</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Policy</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Variant Fulfillment Service</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>Variant Price</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>Variant Compare At Price</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>Variant Requires Shipping</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>Variant Taxable</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>Variant Barcode</t>
         </is>
       </c>
-      <c r="V1" s="10" t="inlineStr">
+      <c r="V1" s="11" t="inlineStr">
         <is>
           <t>Image Src</t>
         </is>
       </c>
-      <c r="W1" s="10" t="inlineStr">
+      <c r="W1" s="11" t="inlineStr">
         <is>
           <t>Image Position</t>
         </is>
       </c>
-      <c r="X1" s="10" t="inlineStr">
+      <c r="X1" s="11" t="inlineStr">
         <is>
           <t>Image Alt Text</t>
         </is>
       </c>
-      <c r="Y1" s="10" t="inlineStr">
+      <c r="Y1" s="11" t="inlineStr">
         <is>
           <t>Gift Card</t>
         </is>
       </c>
-      <c r="Z1" s="10" t="inlineStr">
+      <c r="Z1" s="11" t="inlineStr">
         <is>
           <t>SEO Title</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AA1" s="11" t="inlineStr">
         <is>
           <t>SEO Description</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AB1" s="11" t="inlineStr">
         <is>
           <t>Google Shopping / Google Product Category</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AC1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>crossover-tee-charcoal</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Crossover Active Tee | Charcoal Signature-Fit - Tailored Cut</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Crossover Active Tee | Charcoal Signature-Fit&lt;/strong&gt; by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Cutsclothing (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Cuts Clothing Crossover Active Tee - Charcoal Signature Fit</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Experience the perfect fusion of athletic performance and everyday style with our breathable, curve-hem active tee. Engineered for movement, this shirt keeps you cool and comfortable from your morning workout to your evening commute.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Breathable cotton-forward fabric blend for all-day airflow.&lt;/li&gt;&lt;li&gt;Signature-Fit cut offers a modern, tailored aesthetic without restriction.&lt;/li&gt;&lt;li&gt;Curved-hem design provides an elongated, flattering silhouette.&lt;/li&gt;&lt;li&gt;Tagless interior construction eliminates irritation and chafing.&lt;/li&gt;&lt;li&gt;Versatile moisture-wicking properties for active and casual wear.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;&lt;p&gt;&lt;strong&gt;Material:&lt;/strong&gt; Performance Cotton Blend | &lt;strong&gt;Fit:&lt;/strong&gt; Signature-Fit | &lt;strong&gt;Care:&lt;/strong&gt; Machine Wash Cold&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Cutsclothing</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Shirts &amp; Tops</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Shirts &amp; Tops</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Activewear, T-Shirts, Charcoal, Mens Apparel, Performance Gear</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>CROSSOVER-TEE-CHARCO-FIXED</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>5500.00</t>
         </is>
       </c>
-      <c r="R2" s="11" t="inlineStr"/>
-      <c r="S2" s="11" t="inlineStr">
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T2" s="11" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U2" s="11" t="inlineStr"/>
-      <c r="V2" s="11" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr"/>
+      <c r="V2" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/1368/3463/files/CHARCOAL_CrossoverTee_-4.jpg?v=1786661106</t>
         </is>
       </c>
-      <c r="W2" s="11" t="inlineStr">
+      <c r="W2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X2" s="11" t="inlineStr">
-        <is>
-          <t>Crossover Active Tee | Charcoal Signature-Fit - Cutsclothing Official Product View</t>
-        </is>
-      </c>
-      <c r="Y2" s="11" t="inlineStr">
+      <c r="X2" s="12" t="inlineStr">
+        <is>
+          <t>Model wearing a charcoal Cuts Clothing Crossover Active Tee with a curved hem design</t>
+        </is>
+      </c>
+      <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z2" s="11" t="inlineStr">
-        <is>
-          <t>Crossover Active Tee | Charcoal Signature-Fit - Tailored Cut</t>
-        </is>
-      </c>
-      <c r="AA2" s="11" t="inlineStr">
-        <is>
-          <t>The  Crossover Active Tee | Charcoal Signature-Fit  by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Tho</t>
-        </is>
-      </c>
-      <c r="AB2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC2" s="11" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
+        <is>
+          <t>Cuts Clothing Crossover Active Tee - Charcoal Signature Fit</t>
+        </is>
+      </c>
+      <c r="AA2" s="12" t="inlineStr">
+        <is>
+          <t>Experience the perfect fusion of athletic performance and everyday style with our breathable, curve-hem active tee. Engineered for movement, this shirt kee</t>
+        </is>
+      </c>
+      <c r="AB2" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Shirts &amp; Tops</t>
+        </is>
+      </c>
+      <c r="AC2" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>icon-pull-on-cropped-pant-sepia-tint</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Icon Pull-On Pant | Sepia Tint Classic-Fit Enduratech™ | Handcrafted Artisanal Collection</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Icon Pull-On Pant | Sepia Tint Classic-Fit Enduratech™&lt;/strong&gt; by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Artisanal Craftsmanship:&lt;/strong&gt; Individually crafted using premium, heirloom-grade materials for enduring durability.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Timeless Functional Design:&lt;/strong&gt; Balances modern aesthetics with ergonomic daily utility for home and living spaces.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Sustainable Sourcing:&lt;/strong&gt; Built responsibly with low-impact manufacturing and non-toxic, food-safe finishes.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Signature Heritage Quality:&lt;/strong&gt; Engineered to withstand everyday wear while maintaining distinctive character.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Material / Build&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Heirloom-Grade Materials with Hand-Finished Detailing&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Application&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Daily Residential &amp; Commercial Architectural Use&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care &amp; Maintenance&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Wipe clean with soft damp cloth; food-safe / non-porous&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Cutsclothing (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Design Standard&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Timeless Modern Functionalism&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Cuts Clothing Icon Pull-On Cropped Pant - Sepia Tint</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Upgrade your daily wardrobe with the Icon Pull-On Pant, featuring our proprietary Enduratech fabric for unmatched durability and stretch. This cropped-fit trouser delivers a relaxed, refined look that transitions effortlessly between professional and casual settings.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Enduratech fabric provides premium 4-way stretch and wrinkle resistance.&lt;/li&gt;&lt;li&gt;Modern cropped-leg length offers a contemporary, stylish profile.&lt;/li&gt;&lt;li&gt;Easy-wear pull-on elastic waistband ensures maximum daily comfort.&lt;/li&gt;&lt;li&gt;Durable construction maintains shape through repeated washes.&lt;/li&gt;&lt;li&gt;Deep pockets provide secure storage for your daily essentials.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;&lt;p&gt;&lt;strong&gt;Material:&lt;/strong&gt; Enduratech Fabric | &lt;strong&gt;Fit:&lt;/strong&gt; Classic-Fit Cropped | &lt;strong&gt;Style:&lt;/strong&gt; Pull-On Trouser&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Cutsclothing</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Home &amp; Garden &gt; Furniture</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Home &amp; Garden &gt; Furniture</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Pants</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Pants</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Pants, Casual Wear, Enduratech, Mens Bottoms, Cropped</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>ICON-PULL-ON-CROPPED-FIXED</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>8600.00</t>
         </is>
       </c>
-      <c r="R3" s="11" t="inlineStr"/>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="11" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr"/>
-      <c r="V3" s="11" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr"/>
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/1368/3463/files/SEPIATINT_IconPull-OnPant_0631.jpg?v=1791397956</t>
         </is>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X3" s="11" t="inlineStr">
-        <is>
-          <t>Icon Pull-On Pant | Sepia Tint Classic-Fit Enduratech™ - Cutsclothing Official Product View</t>
-        </is>
-      </c>
-      <c r="Y3" s="11" t="inlineStr">
+      <c r="X3" s="12" t="inlineStr">
+        <is>
+          <t>Cuts Clothing Icon Pull-On Cropped Pant in Sepia Tint colorway</t>
+        </is>
+      </c>
+      <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z3" s="11" t="inlineStr">
-        <is>
-          <t>Icon Pull-On Pant | Sepia Tint Classic-Fit Enduratech™ | Handcrafted Artisanal Collection</t>
-        </is>
-      </c>
-      <c r="AA3" s="11" t="inlineStr">
-        <is>
-          <t>The  Icon Pull-On Pant | Sepia Tint Classic-Fit Enduratech™  by Cutsclothing represents the highest standard of intentional craftsmanship and functional de</t>
-        </is>
-      </c>
-      <c r="AB3" s="11" t="inlineStr">
-        <is>
-          <t>Home &amp; Garden &gt; Furniture</t>
-        </is>
-      </c>
-      <c r="AC3" s="11" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
+        <is>
+          <t>Cuts Clothing Icon Pull-On Cropped Pant - Sepia Tint</t>
+        </is>
+      </c>
+      <c r="AA3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upgrade your daily wardrobe with the Icon Pull-On Pant, featuring our proprietary Enduratech fabric for unmatched durability and stretch. This cropped-fit </t>
+        </is>
+      </c>
+      <c r="AB3" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Pants</t>
+        </is>
+      </c>
+      <c r="AC3" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>ao-l-s-polo-white</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>AO Long Sleeve Polo | White Signature-Fit PYCA Pro® - Tailored Cut</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;AO Long Sleeve Polo | White Signature-Fit PYCA Pro®&lt;/strong&gt; by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Cutsclothing (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Cuts Clothing AO Long Sleeve Polo - White PYCA Pro</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Achieve a polished look that never compromises on comfort with the versatile AO Long Sleeve Polo. Crafted from high-performance PYCA Pro fabric, this essential piece resists wrinkles and keeps you looking sharp from morning meetings to weekend events.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;PYCA Pro fabric offers lightweight comfort and professional structure.&lt;/li&gt;&lt;li&gt;Wrinkle-resistant material ensures a crisp look throughout the day.&lt;/li&gt;&lt;li&gt;Long sleeve design provides excellent coverage and layering versatility.&lt;/li&gt;&lt;li&gt;Signature-Fit tailoring creates a sleek, flattering profile.&lt;/li&gt;&lt;li&gt;Minimalist aesthetic pairs perfectly with trousers or denim.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;&lt;p&gt;&lt;strong&gt;Material:&lt;/strong&gt; PYCA Pro | &lt;strong&gt;Fit:&lt;/strong&gt; Signature-Fit | &lt;strong&gt;Style:&lt;/strong&gt; Long Sleeve Polo&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Cutsclothing</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Shirts &amp; Tops</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Shirts &amp; Tops</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Polos, Long Sleeve, White, Mens Apparel, Business Casual</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>AO-L-S-POLO-WHITE-FIXED</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>6500.00</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/1368/3463/files/WHITE_AOLSPolo_f9563db7-dac1-41ef-ae57-7ec1cbd215a0.jpg?v=1785801354</t>
         </is>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X4" s="11" t="inlineStr">
-        <is>
-          <t>AO Long Sleeve Polo | White Signature-Fit PYCA Pro® - Cutsclothing Official Product View</t>
-        </is>
-      </c>
-      <c r="Y4" s="11" t="inlineStr">
+      <c r="X4" s="12" t="inlineStr">
+        <is>
+          <t>Cuts Clothing white AO long sleeve polo shirt featuring PYCA Pro fabric</t>
+        </is>
+      </c>
+      <c r="Y4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
-        <is>
-          <t>AO Long Sleeve Polo | White Signature-Fit PYCA Pro® - Tailored Cut</t>
-        </is>
-      </c>
-      <c r="AA4" s="11" t="inlineStr">
-        <is>
-          <t>The  AO Long Sleeve Polo | White Signature-Fit PYCA Pro®  by Cutsclothing represents the highest standard of intentional craftsmanship and functional desig</t>
-        </is>
-      </c>
-      <c r="AB4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC4" s="11" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
+        <is>
+          <t>Cuts Clothing AO Long Sleeve Polo - White PYCA Pro</t>
+        </is>
+      </c>
+      <c r="AA4" s="12" t="inlineStr">
+        <is>
+          <t>Achieve a polished look that never compromises on comfort with the versatile AO Long Sleeve Polo. Crafted from high-performance PYCA Pro fabric, this essen</t>
+        </is>
+      </c>
+      <c r="AB4" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Shirts &amp; Tops</t>
+        </is>
+      </c>
+      <c r="AC4" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>womens-divine-fleece-oversized-hoodie-q-zip-sweatpant-fit-bundle</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>The 9-to-Cozy Fit: Oversized - Tailored Cut</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;The 9-to-Cozy Fit: Oversized&lt;/strong&gt; by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Cutsclothing (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Cuts Women's 9-to-Cozy Fleece Oversized Bundle</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Elevate your lounge rotation with the full Divine Fleece set, designed for maximum softness and a relaxed oversized fit. This curated bundle gives you the ultimate matching comfort experience while offering exceptional value.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Buttery-soft fleece material provides premium warmth and comfort.&lt;/li&gt;&lt;li&gt;Bundle includes oversized hoodie, quarter-zip, and matching sweatpants.&lt;/li&gt;&lt;li&gt;Relaxed, modern cut designed for high-end lounging and layering.&lt;/li&gt;&lt;li&gt;Versatile separates that can be styled individually or as a set.&lt;/li&gt;&lt;li&gt;High-quality fabric construction designed for lasting softness.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;&lt;p&gt;&lt;strong&gt;Material:&lt;/strong&gt; Divine Fleece | &lt;strong&gt;Fit:&lt;/strong&gt; Oversized | &lt;strong&gt;Bundle:&lt;/strong&gt; 3-Piece Set&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Cutsclothing</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Clothing Sets</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Clothing Sets</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Womenswear, Lounge Sets, Fleece, Bundle, Oversized</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>WOMENS-DIVINE-FLEECE-FIXED</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>20500.00</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="11" t="inlineStr">
+      <c r="U5" s="12" t="inlineStr"/>
+      <c r="V5" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/1368/3463/files/CHARCOAL_DivineFleeceQ-Zip_2_78664f41-1de5-4b10-a6f9-59c88009f8f5.jpg?v=1793044802</t>
         </is>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" s="11" t="inlineStr">
-        <is>
-          <t>The 9-to-Cozy Fit: Oversized - Cutsclothing Official Product View</t>
-        </is>
-      </c>
-      <c r="Y5" s="11" t="inlineStr">
+      <c r="X5" s="12" t="inlineStr">
+        <is>
+          <t>Women's 9-to-Cozy bundle featuring Divine Fleece hoodie, quarter-zip, and sweatpants</t>
+        </is>
+      </c>
+      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z5" s="11" t="inlineStr">
-        <is>
-          <t>The 9-to-Cozy Fit: Oversized - Tailored Cut</t>
-        </is>
-      </c>
-      <c r="AA5" s="11" t="inlineStr">
-        <is>
-          <t>The  The 9-to-Cozy Fit: Oversized  by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully enginee</t>
-        </is>
-      </c>
-      <c r="AB5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC5" s="11" t="inlineStr">
+      <c r="Z5" s="12" t="inlineStr">
+        <is>
+          <t>Cuts Women's 9-to-Cozy Fleece Oversized Bundle</t>
+        </is>
+      </c>
+      <c r="AA5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elevate your lounge rotation with the full Divine Fleece set, designed for maximum softness and a relaxed oversized fit. This curated bundle gives you the </t>
+        </is>
+      </c>
+      <c r="AB5" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Clothing Sets</t>
+        </is>
+      </c>
+      <c r="AC5" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>overtime-boxed-tee-foundation-air-fit-bundle</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The Overtime Fit: Boxed Crop Tee + Foundation-Air Trouser - Tailored Cut</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;The Overtime Fit: Boxed Crop Tee + Foundation-Air Trouser&lt;/strong&gt; by Cutsclothing represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Cutsclothing (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Cuts The Overtime Fit: Boxed Tee &amp; Pleated Trouser Bundle</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Master the art of effortless, elevated style with this hand-picked lookbook ensemble featuring our signature Boxed Crop Tee and Foundation-Air Trouser. This sharp, minimalist combination is designed to make dressing for any occasion perfectly simple.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Curated bundle includes the Boxed Crop Tee and Relaxed Pleated Trouser.&lt;/li&gt;&lt;li&gt;Foundation-Air fabric offers lightweight, breathable performance.&lt;/li&gt;&lt;li&gt;Boxed Crop Tee silhouette creates a modern, structured aesthetic.&lt;/li&gt;&lt;li&gt;Pleated trousers provide a sophisticated, relaxed professional look.&lt;/li&gt;&lt;li&gt;Pre-styled combination saves time and ensures a cohesive outfit.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;&lt;p&gt;&lt;strong&gt;Material:&lt;/strong&gt; Foundation-Air / Signature Fabric | &lt;strong&gt;Fit:&lt;/strong&gt; Relaxed / Boxed | &lt;strong&gt;Style:&lt;/strong&gt; Elevated Casual&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Cutsclothing</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Clothing Sets</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Clothing Sets</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Menswear, Bundles, Pleated Pants, Crop Tee, Streetwear</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>OVERTIME-BOXED-TEE-F-FIXED</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>17200.00</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
+      <c r="T6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr">
+      <c r="U6" s="12" t="inlineStr"/>
+      <c r="V6" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/1368/3463/files/fw26-lookbook-DSCF6529-overtime-3x4.jpg?v=1793033510</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X6" s="11" t="inlineStr">
-        <is>
-          <t>The Overtime Fit: Boxed Crop Tee + Foundation-Air Trouser - Cutsclothing Official Product View</t>
-        </is>
-      </c>
-      <c r="Y6" s="11" t="inlineStr">
+      <c r="X6" s="12" t="inlineStr">
+        <is>
+          <t>Full outfit bundle featuring the Overtime Boxed Crop Tee and Foundation-Air Pleated Trousers</t>
+        </is>
+      </c>
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z6" s="11" t="inlineStr">
-        <is>
-          <t>The Overtime Fit: Boxed Crop Tee + Foundation-Air Trouser - Tailored Cut</t>
-        </is>
-      </c>
-      <c r="AA6" s="11" t="inlineStr">
-        <is>
-          <t>The  The Overtime Fit: Boxed Crop Tee + Foundation-Air Trouser  by Cutsclothing represents the highest standard of intentional craftsmanship and functional</t>
-        </is>
-      </c>
-      <c r="AB6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC6" s="11" t="inlineStr">
+      <c r="Z6" s="12" t="inlineStr">
+        <is>
+          <t>Cuts The Overtime Fit: Boxed Tee &amp; Pleated Trouser Bundle</t>
+        </is>
+      </c>
+      <c r="AA6" s="12" t="inlineStr">
+        <is>
+          <t>Master the art of effortless, elevated style with this hand-picked lookbook ensemble featuring our signature Boxed Crop Tee and Foundation-Air Trouser. Thi</t>
+        </is>
+      </c>
+      <c r="AB6" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing &gt; Clothing Sets</t>
+        </is>
+      </c>
+      <c r="AC6" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
